--- a/data/trans_dic/Hacinamiento_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/Hacinamiento_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación</t>
+          <t>Hogares con dos o más personas por habitación (tasa de respuesta: 99,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,34; 5,15</t>
+          <t>2,23; 5,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,18; 6,38</t>
+          <t>3,27; 6,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,17; 6,76</t>
+          <t>3,14; 6,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 5,26</t>
+          <t>0,59; 4,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,9; 7,41</t>
+          <t>3,78; 7,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,89; 6,01</t>
+          <t>2,9; 6,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,83; 5,77</t>
+          <t>2,76; 5,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,64</t>
+          <t>0,93; 2,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,34; 5,67</t>
+          <t>3,35; 5,9</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,43; 5,64</t>
+          <t>3,37; 5,62</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,31; 5,59</t>
+          <t>3,32; 5,63</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,32</t>
+          <t>0,98; 3,2</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,56; 7,63</t>
+          <t>4,32; 7,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,31; 5,92</t>
+          <t>3,37; 5,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,47; 4,99</t>
+          <t>2,58; 4,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,84</t>
+          <t>0,82; 2,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,02; 8,29</t>
+          <t>5,08; 8,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,57; 7,57</t>
+          <t>4,65; 7,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,04; 5,44</t>
+          <t>2,94; 5,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,26</t>
+          <t>1,43; 3,27</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,1; 7,44</t>
+          <t>5,09; 7,39</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,38; 6,35</t>
+          <t>4,33; 6,32</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,91; 4,65</t>
+          <t>3,04; 4,83</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,65</t>
+          <t>1,21; 2,64</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,29; 5,27</t>
+          <t>2,29; 5,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,23; 7,97</t>
+          <t>4,45; 8,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,47; 8,33</t>
+          <t>4,27; 7,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,73</t>
+          <t>1,83; 4,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,99; 7,79</t>
+          <t>4,05; 7,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,27; 11,69</t>
+          <t>7,54; 11,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,84; 8,36</t>
+          <t>4,87; 8,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 4,99</t>
+          <t>1,33; 5,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,56; 5,99</t>
+          <t>3,55; 5,94</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,24; 9,25</t>
+          <t>6,37; 9,3</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,09; 7,64</t>
+          <t>4,99; 7,62</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,22</t>
+          <t>1,8; 4,41</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,22; 7,29</t>
+          <t>4,12; 7,18</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,94; 5,45</t>
+          <t>2,86; 5,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,7</t>
+          <t>2,34; 4,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,35</t>
+          <t>1,79; 4,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,69; 7,85</t>
+          <t>4,71; 7,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,1; 7,01</t>
+          <t>4,11; 6,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,83; 5,33</t>
+          <t>2,83; 5,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,06</t>
+          <t>2,05; 4,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,92; 7,09</t>
+          <t>4,87; 6,99</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,82; 5,72</t>
+          <t>3,87; 5,74</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,84; 4,57</t>
+          <t>2,8; 4,51</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,19; 3,71</t>
+          <t>2,25; 3,85</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,04; 5,6</t>
+          <t>4,1; 5,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,11; 5,66</t>
+          <t>4,04; 5,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,63; 5,08</t>
+          <t>3,6; 4,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,07</t>
+          <t>1,63; 2,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,17; 6,9</t>
+          <t>5,14; 6,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,43; 7,05</t>
+          <t>5,38; 7,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,87; 5,34</t>
+          <t>3,92; 5,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,92; 3,13</t>
+          <t>1,89; 3,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,86; 6,03</t>
+          <t>4,87; 6,02</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,92; 6,06</t>
+          <t>5,01; 6,05</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,92; 4,93</t>
+          <t>3,93; 4,93</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,94; 2,84</t>
+          <t>1,93; 2,84</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación</t>
+          <t>Hogares con dos o más personas por habitación (tasa de respuesta: 99,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>16171; 35618</t>
+          <t>15440; 36499</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22293; 44772</t>
+          <t>22957; 45602</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21374; 45513</t>
+          <t>21122; 45902</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3989; 33147</t>
+          <t>3705; 31247</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26805; 50927</t>
+          <t>25978; 50878</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20013; 41642</t>
+          <t>20120; 42538</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19046; 38770</t>
+          <t>18552; 39768</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6201; 19059</t>
+          <t>6670; 19238</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>46023; 78181</t>
+          <t>46147; 81386</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>47809; 78579</t>
+          <t>47035; 78392</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44542; 75214</t>
+          <t>44632; 75707</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13793; 44844</t>
+          <t>13197; 43152</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>43674; 73105</t>
+          <t>41402; 71209</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33620; 60061</t>
+          <t>34223; 60714</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25135; 50763</t>
+          <t>26262; 50406</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9226; 33570</t>
+          <t>9764; 34379</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>48547; 80060</t>
+          <t>49095; 83584</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>47091; 78045</t>
+          <t>47948; 79047</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31578; 56512</t>
+          <t>30489; 56144</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13908; 30879</t>
+          <t>13521; 30981</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>98116; 143144</t>
+          <t>97928; 142213</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>89686; 129926</t>
+          <t>88554; 129366</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>59897; 95643</t>
+          <t>62445; 99358</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25662; 56580</t>
+          <t>25846; 56382</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15546; 35680</t>
+          <t>15506; 37135</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>31844; 59995</t>
+          <t>33529; 62761</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33740; 62856</t>
+          <t>32188; 58718</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12650; 33185</t>
+          <t>12841; 33165</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>27275; 53182</t>
+          <t>27697; 51812</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>56183; 90344</t>
+          <t>58302; 90729</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37767; 65306</t>
+          <t>37989; 65039</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12995; 46168</t>
+          <t>12317; 47650</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>48475; 81435</t>
+          <t>48364; 80865</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>95179; 141122</t>
+          <t>97277; 141870</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>78126; 117360</t>
+          <t>76647; 116988</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>29604; 68627</t>
+          <t>29227; 71679</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39687; 68460</t>
+          <t>38679; 67463</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27766; 51490</t>
+          <t>27065; 50840</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21345; 43685</t>
+          <t>21774; 42129</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17576; 39930</t>
+          <t>16396; 38302</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>48471; 81182</t>
+          <t>48688; 80652</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>42866; 73400</t>
+          <t>43060; 72689</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29321; 55124</t>
+          <t>29261; 52958</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21716; 43965</t>
+          <t>22235; 43468</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>97121; 139982</t>
+          <t>96080; 137996</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>75994; 113946</t>
+          <t>77077; 114357</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>55852; 89715</t>
+          <t>54996; 88492</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>43839; 74243</t>
+          <t>45036; 76978</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>132020; 183004</t>
+          <t>133944; 187136</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>140369; 193221</t>
+          <t>137796; 188694</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>122364; 171312</t>
+          <t>121449; 167990</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>56636; 105425</t>
+          <t>56103; 100191</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>174184; 232663</t>
+          <t>173320; 231291</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>192329; 250007</t>
+          <t>190703; 249600</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>136608; 188378</t>
+          <t>138065; 189847</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>70590; 114945</t>
+          <t>69417; 114009</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>322844; 400050</t>
+          <t>323144; 399602</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>342485; 421320</t>
+          <t>348380; 421226</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>270698; 340004</t>
+          <t>270888; 339895</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>137769; 201908</t>
+          <t>136957; 201799</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Hacinamiento_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/Hacinamiento_R-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,23; 5,28</t>
+          <t>2,28; 5,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,27; 6,5</t>
+          <t>3,2; 6,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,14; 6,81</t>
+          <t>3,18; 6,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 4,96</t>
+          <t>0,63; 4,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,78; 7,4</t>
+          <t>3,79; 7,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,9; 6,14</t>
+          <t>2,81; 5,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,76; 5,92</t>
+          <t>2,75; 5,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,67</t>
+          <t>1,12; 2,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,35; 5,9</t>
+          <t>3,4; 5,66</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,37; 5,62</t>
+          <t>3,42; 5,66</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,32; 5,63</t>
+          <t>3,41; 5,69</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,2</t>
+          <t>1,02; 2,82</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,32; 7,43</t>
+          <t>4,36; 7,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,37; 5,98</t>
+          <t>3,45; 6,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,58; 4,95</t>
+          <t>2,59; 5,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,9</t>
+          <t>1,69; 3,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,08; 8,65</t>
+          <t>5,04; 8,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,65; 7,67</t>
+          <t>4,62; 7,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,94; 5,41</t>
+          <t>3,01; 5,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,43; 3,27</t>
+          <t>1,71; 3,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,09; 7,39</t>
+          <t>5,15; 7,43</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,33; 6,32</t>
+          <t>4,37; 6,42</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,04; 4,83</t>
+          <t>2,96; 4,73</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,64</t>
+          <t>1,85; 3,23</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,29; 5,48</t>
+          <t>2,29; 5,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,45; 8,34</t>
+          <t>4,63; 8,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,27; 7,78</t>
+          <t>4,26; 8,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,73</t>
+          <t>2,42; 5,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,05; 7,59</t>
+          <t>3,97; 7,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,54; 11,74</t>
+          <t>7,39; 11,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,87; 8,33</t>
+          <t>4,96; 8,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 5,15</t>
+          <t>3,78; 7,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,55; 5,94</t>
+          <t>3,49; 5,92</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,37; 9,3</t>
+          <t>6,48; 9,48</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,99; 7,62</t>
+          <t>5,04; 7,7</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,8; 4,41</t>
+          <t>3,39; 5,69</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,12; 7,18</t>
+          <t>4,28; 7,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,86; 5,38</t>
+          <t>2,92; 5,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,34; 4,54</t>
+          <t>2,25; 4,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,18</t>
+          <t>2,05; 4,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,71; 7,8</t>
+          <t>4,76; 7,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,11; 6,94</t>
+          <t>4,15; 6,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,83; 5,12</t>
+          <t>2,76; 5,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,05; 4,01</t>
+          <t>2,61; 4,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,87; 6,99</t>
+          <t>4,82; 7,0</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,87; 5,74</t>
+          <t>3,89; 5,8</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,8; 4,51</t>
+          <t>2,86; 4,58</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,25; 3,85</t>
+          <t>2,62; 4,23</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,1; 5,73</t>
+          <t>4,08; 5,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,04; 5,53</t>
+          <t>4,1; 5,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,6; 4,98</t>
+          <t>3,6; 5,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,92</t>
+          <t>2,18; 3,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,14; 6,86</t>
+          <t>5,18; 6,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,38; 7,04</t>
+          <t>5,45; 7,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,92; 5,38</t>
+          <t>3,85; 5,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 3,1</t>
+          <t>2,75; 3,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,87; 6,02</t>
+          <t>4,81; 5,94</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,01; 6,05</t>
+          <t>4,95; 6,06</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,93; 4,93</t>
+          <t>3,91; 4,93</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,93; 2,84</t>
+          <t>2,63; 3,45</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10520</t>
+          <t>10922</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11458</t>
+          <t>13700</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21978</t>
+          <t>24622</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>15440; 36499</t>
+          <t>15784; 36851</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>22957; 45602</t>
+          <t>22461; 44985</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21122; 45902</t>
+          <t>21416; 46282</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3705; 31247</t>
+          <t>4338; 27405</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>25978; 50878</t>
+          <t>26044; 49962</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20120; 42538</t>
+          <t>19495; 41424</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18552; 39768</t>
+          <t>18486; 39411</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6670; 19238</t>
+          <t>8151; 21388</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>46147; 81386</t>
+          <t>46872; 77948</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>47035; 78392</t>
+          <t>47759; 78922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44632; 75707</t>
+          <t>45860; 76513</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13197; 43152</t>
+          <t>14477; 39921</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20286</t>
+          <t>27380</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>20553</t>
+          <t>25355</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>40838</t>
+          <t>52735</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41402; 71209</t>
+          <t>41774; 71379</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34223; 60714</t>
+          <t>35050; 62288</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26262; 50406</t>
+          <t>26344; 52351</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9764; 34379</t>
+          <t>17556; 40741</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>49095; 83584</t>
+          <t>48677; 81270</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>47948; 79047</t>
+          <t>47686; 80419</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30489; 56144</t>
+          <t>31234; 57414</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13521; 30981</t>
+          <t>18065; 34991</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>97928; 142213</t>
+          <t>99014; 143042</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>88554; 129366</t>
+          <t>89393; 131367</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>62445; 99358</t>
+          <t>60910; 97254</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25846; 56382</t>
+          <t>38725; 67807</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20601</t>
+          <t>28298</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27373</t>
+          <t>42412</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>47975</t>
+          <t>70711</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15506; 37135</t>
+          <t>15535; 36153</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>33529; 62761</t>
+          <t>34896; 61679</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32188; 58718</t>
+          <t>32161; 60336</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12841; 33165</t>
+          <t>19346; 40371</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>27697; 51812</t>
+          <t>27088; 52553</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>58302; 90729</t>
+          <t>57144; 91080</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37989; 65039</t>
+          <t>38690; 65682</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12317; 47650</t>
+          <t>30373; 60850</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>48364; 80865</t>
+          <t>47521; 80548</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>97277; 141870</t>
+          <t>98922; 144628</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>76647; 116988</t>
+          <t>77372; 118278</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>29227; 71679</t>
+          <t>54404; 91256</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26442</t>
+          <t>29764</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>31602</t>
+          <t>39144</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>58043</t>
+          <t>68908</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>38679; 67463</t>
+          <t>40251; 68820</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27065; 50840</t>
+          <t>27544; 51400</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21774; 42129</t>
+          <t>20858; 43096</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>16396; 38302</t>
+          <t>20117; 42738</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>48688; 80652</t>
+          <t>49204; 81205</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>43060; 72689</t>
+          <t>43389; 71288</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29261; 52958</t>
+          <t>28577; 53817</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>22235; 43468</t>
+          <t>28893; 51091</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>96080; 137996</t>
+          <t>95071; 138191</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>77077; 114357</t>
+          <t>77495; 115555</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>54996; 88492</t>
+          <t>56237; 89876</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>45036; 76978</t>
+          <t>54750; 88390</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>77848</t>
+          <t>96365</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>90986</t>
+          <t>120611</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>168834</t>
+          <t>216975</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>133944; 187136</t>
+          <t>133114; 185742</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>137796; 188694</t>
+          <t>139961; 188220</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>121449; 167990</t>
+          <t>121365; 171510</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>56103; 100191</t>
+          <t>76391; 118263</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>173320; 231291</t>
+          <t>174603; 230064</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>190703; 249600</t>
+          <t>193119; 250564</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>138065; 189847</t>
+          <t>135844; 185701</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>69417; 114009</t>
+          <t>101730; 144358</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>323144; 399602</t>
+          <t>319328; 394110</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>348380; 421226</t>
+          <t>344656; 421901</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>270888; 339895</t>
+          <t>270054; 339993</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>136957; 201799</t>
+          <t>189584; 248382</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Hacinamiento_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/Hacinamiento_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación (tasa de respuesta: 99,44%)</t>
+          <t>Población en cuya vivienda residen dos o más personas por habitación (tasa de respuesta: 99,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación (tasa de respuesta: 99,44%)</t>
+          <t>Población en cuya vivienda residen dos o más personas por habitación (tasa de respuesta: 99,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
